--- a/reports/一级子公司B_利润表_2025-07.xlsx
+++ b/reports/一级子公司B_利润表_2025-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>53810849</v>
+        <v>71391391</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>15888279</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>98581134</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>223290</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>1387607</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>201439</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>1248680</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>168287</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1040503</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>157414</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>971159</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>90087</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>555005</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>67603</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>416322</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>53810849</v>
+        <v>70483271</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>14980159</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8976758</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>55540354</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1343150</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>8331839</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>669968</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>4165973</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4458122</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>27771206</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>445364</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>2776728</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>334035</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>2082156</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>557321</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>3469562</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>446711</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>2775155</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>53730649</v>
+        <v>53735006</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>333103021</v>
+        <v>332976992</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>80200</v>
+        <v>80162</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>560181</v>
+        <v>559832</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1012200</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>6243226</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>675744</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4162623</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>49662356</v>
+        <v>64076825</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>28273394</v>
+        <v>36137862</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>167140</v>
+        <v>8094551</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1040121</v>
+        <v>49979586</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28106254</v>
+        <v>28043311</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>173611037</v>
+        <v>173566517</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1678375</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>10414865</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>535820</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3332762</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>334296</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2082809</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>400805</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2498998</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>300657</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1873890</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>200678</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1249010</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>167567</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1040663</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1336732</v>
+        <v>1343828</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8320611</v>
+        <v>8324331</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>44990</v>
+        <v>44905</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>277797</v>
+        <v>277467</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2792743</v>
+        <v>2812328</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>17342175</v>
+        <v>17342485</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>16810938</v>
+        <v>16895548</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>104114758</v>
+        <v>104067627</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2816719</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>17347672</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>448549</v>
+        <v>452342</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3148653</v>
+        <v>3149497</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401888</v>
+        <v>401408</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2801818</v>
+        <v>2799973</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>29830</v>
+        <v>30037</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>209833</v>
+        <v>210031</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134825</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>945255</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>292945</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1822593</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>89528</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>630231</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67096</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>472650</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>111863</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>787672</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>418174</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2602038</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>59864</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>419968</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45009</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>314930</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>75199</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>524831</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52743</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>367365</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37717</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>262408</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30178</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>209945</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22613</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>157477</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>4148493</v>
+        <v>7402474</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-131930</v>
+        <v>4990611</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>167727</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1041496</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37356</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>262594</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>59689</v>
+        <v>59676</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>419697</v>
+        <v>420153</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>4088804</v>
+        <v>7510525</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1789319</v>
+        <v>1790028</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>12589273</v>
+        <v>12602530</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2299485</v>
+        <v>5720497</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2299485</v>
+        <v>5720497</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>2299485</v>
+        <v>5720497</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2299485</v>
+        <v>5720497</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2299485</v>
+        <v>5720497</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
